--- a/data/case-study-a-clinical-trial--clinical_trial.xlsx
+++ b/data/case-study-a-clinical-trial--clinical_trial.xlsx
@@ -4751,7 +4751,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WHAT IS CAPTURED: a randomized controlled trial of an LDL-lowering drug, one row per patient.</t>
+          <t>WHAT IS CAPTURED: a randomized controlled trial of an LDL-lowering drug, one row per patient (a realistic teaching dataset written for the book).</t>
         </is>
       </c>
     </row>
